--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\Model_Demo_Adv_Veda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7B32299-3A73-42FE-AAE3-E05D4DC79CB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F74337-5219-4FB4-BD51-000044AE07C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="853" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" tabRatio="853" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Region-Time Slices" sheetId="16" r:id="rId1"/>
@@ -327,7 +327,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="322">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -1247,21 +1247,12 @@
     <t>worksheet</t>
   </si>
   <si>
-    <t>table</t>
-  </si>
-  <si>
     <t>row</t>
   </si>
   <si>
     <t>column</t>
   </si>
   <si>
-    <t>multi-row table with a header</t>
-  </si>
-  <si>
-    <t>~md_t</t>
-  </si>
-  <si>
     <t>single block (could be multi-col/row)</t>
   </si>
   <si>
@@ -1289,52 +1280,19 @@
     <t>scope</t>
   </si>
   <si>
-    <t>~md-v_w</t>
-  </si>
-  <si>
-    <t>~md-v_s</t>
-  </si>
-  <si>
-    <t>~md-v_r</t>
-  </si>
-  <si>
-    <t>~md-v_c</t>
-  </si>
-  <si>
-    <t>Column</t>
-  </si>
-  <si>
-    <t>Valid entries</t>
-  </si>
-  <si>
-    <t>Remarks</t>
-  </si>
-  <si>
-    <t>Location</t>
-  </si>
-  <si>
-    <t>=&lt;top left cell&gt;</t>
-  </si>
-  <si>
-    <t>Location2</t>
-  </si>
-  <si>
-    <t>=&lt;bottom right cell&gt;</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Table/Row/Column/Cell</t>
-  </si>
-  <si>
-    <t>&lt;metadata dimension&gt;</t>
-  </si>
-  <si>
-    <t>that is defined in ~md_dimensions</t>
-  </si>
-  <si>
     <t>…</t>
+  </si>
+  <si>
+    <t>&lt;tilde&gt;md-v_w</t>
+  </si>
+  <si>
+    <t>&lt;tilde&gt;md-v_s</t>
+  </si>
+  <si>
+    <t>&lt;tilde&gt;md-v_r</t>
+  </si>
+  <si>
+    <t>&lt;tilde&gt;md-v_c</t>
   </si>
 </sst>
 </file>
@@ -1361,7 +1319,7 @@
     <numFmt numFmtId="178" formatCode="_-* #,##0.00\ _F_-;\-* #,##0.00\ _F_-;_-* &quot;-&quot;??\ _F_-;_-@_-"/>
     <numFmt numFmtId="179" formatCode="#,##0.0;\-#,##0.0;&quot;-&quot;"/>
   </numFmts>
-  <fonts count="69">
+  <fonts count="67">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -1781,22 +1739,6 @@
       <name val="Tahoma"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="58">
     <fill>
@@ -2116,7 +2058,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -2445,26 +2387,8 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="437">
+  <cellStyleXfs count="435">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="20" fillId="8" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="15" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -3012,10 +2936,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="29" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="127">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -3300,11 +3222,8 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="431" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="64" fillId="0" borderId="0" xfId="431" applyFont="1"/>
     <xf numFmtId="0" fontId="63" fillId="0" borderId="0" xfId="421"/>
-    <xf numFmtId="0" fontId="67" fillId="0" borderId="28" xfId="435"/>
-    <xf numFmtId="0" fontId="68" fillId="0" borderId="29" xfId="436"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
-  <cellStyles count="437">
+  <cellStyles count="435">
     <cellStyle name="20% - Accent1 2" xfId="9" xr:uid="{868B5B88-E909-4783-AD13-DE2EB64A3CB4}"/>
     <cellStyle name="20% - Accent1 3" xfId="10" xr:uid="{61BBC959-7746-45BD-8177-E58B91071E9A}"/>
     <cellStyle name="20% - Accent2 2" xfId="11" xr:uid="{84EF0E0D-0CC7-40A8-A781-F5D8904EB610}"/>
@@ -3486,9 +3405,7 @@
     <cellStyle name="Good 2" xfId="187" xr:uid="{BB37B930-94A2-48EF-AF7B-C42475492154}"/>
     <cellStyle name="Heading" xfId="188" xr:uid="{5837C8E7-E8F7-4B5A-AFD0-01AF38EAA282}"/>
     <cellStyle name="Heading 1 2" xfId="189" xr:uid="{209321B4-9C5A-4EDB-A85D-010D1C6C4025}"/>
-    <cellStyle name="Heading 2" xfId="435" builtinId="17"/>
     <cellStyle name="Heading 2 2" xfId="190" xr:uid="{F2B40050-2B0C-4441-82A4-7207EE99CE0F}"/>
-    <cellStyle name="Heading 3" xfId="436" builtinId="18"/>
     <cellStyle name="Heading 3 2" xfId="191" xr:uid="{81A82C4F-F140-4055-B559-5F1DA28E4FE6}"/>
     <cellStyle name="Heading 4 2" xfId="192" xr:uid="{363D0A0E-394F-4ACF-9AEC-36F2FF4285FE}"/>
     <cellStyle name="Heading 5" xfId="193" xr:uid="{9735A0D9-49F9-4F43-B1E1-07F6390141C9}"/>
@@ -8044,7 +7961,7 @@
         <v>180</v>
       </c>
       <c r="D8" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E8" t="s">
         <v>182</v>
@@ -9267,16 +9184,16 @@
     </row>
     <row r="20" spans="3:10">
       <c r="C20" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J20" s="120"/>
     </row>
     <row r="21" spans="3:10">
       <c r="C21" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D21" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J21" s="120"/>
     </row>
@@ -9285,7 +9202,7 @@
         <v>299</v>
       </c>
       <c r="D22" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="23" spans="3:10">
@@ -9293,7 +9210,7 @@
         <v>300</v>
       </c>
       <c r="D23" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="24" spans="3:10">
@@ -9301,7 +9218,7 @@
         <v>301</v>
       </c>
       <c r="D24" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="25" spans="3:10">
@@ -9309,15 +9226,15 @@
         <v>302</v>
       </c>
       <c r="D25" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="26" spans="3:10">
       <c r="C26" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D26" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
     </row>
     <row r="27" spans="3:10" ht="13.15">
@@ -9327,126 +9244,59 @@
     </row>
     <row r="30" spans="3:10">
       <c r="C30" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D30" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
     </row>
     <row r="31" spans="3:10">
       <c r="C31" s="14" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>304</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="32" spans="3:10">
       <c r="C32" s="14" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>305</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="33" spans="3:5">
       <c r="C33" s="14" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
     <row r="34" spans="3:5">
       <c r="C34" s="14" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="D34" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="E34" s="14" t="s">
         <v>308</v>
-      </c>
-      <c r="E34" s="14" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="35" spans="3:5">
-      <c r="C35" s="14" t="s">
-        <v>310</v>
-      </c>
-      <c r="D35" s="14" t="s">
-        <v>306</v>
-      </c>
-      <c r="E35" s="119" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="38" spans="3:5" ht="17.25" thickBot="1">
-      <c r="C38" s="124" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="39" spans="3:5" ht="15" thickTop="1" thickBot="1">
-      <c r="C39" s="125" t="s">
-        <v>324</v>
-      </c>
-      <c r="D39" s="125" t="s">
-        <v>325</v>
-      </c>
-      <c r="E39" s="125" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="40" spans="3:5">
-      <c r="C40" t="s">
-        <v>327</v>
-      </c>
-      <c r="D40" s="126" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="41" spans="3:5">
-      <c r="C41" t="s">
-        <v>329</v>
-      </c>
-      <c r="D41" s="126" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="42" spans="3:5">
-      <c r="C42" t="s">
-        <v>331</v>
-      </c>
-      <c r="D42" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="43" spans="3:5">
-      <c r="C43" t="s">
-        <v>333</v>
-      </c>
-      <c r="E43" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="44" spans="3:5">
-      <c r="C44" t="s">
-        <v>333</v>
-      </c>
-      <c r="E44" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="45" spans="3:5">
       <c r="C45" t="s">
-        <v>335</v>
+        <v>317</v>
       </c>
     </row>
   </sheetData>

--- a/SysSettings.xlsx
+++ b/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\Model_Demo_Adv_Veda\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F74337-5219-4FB4-BD51-000044AE07C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0922B367-4F8D-4E39-8F43-E4B4A5CC2F86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="15675" tabRatio="853" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -233,7 +233,7 @@
     <author>Amit Kanudia</author>
   </authors>
   <commentList>
-    <comment ref="C27" authorId="0" shapeId="0" xr:uid="{8E2BCF16-74D8-47B1-9928-4E547A302406}">
+    <comment ref="C28" authorId="0" shapeId="0" xr:uid="{8E2BCF16-74D8-47B1-9928-4E547A302406}">
       <text>
         <r>
           <rPr>
@@ -327,7 +327,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="323">
   <si>
     <t>~TFM_UPD</t>
   </si>
@@ -1293,6 +1293,9 @@
   </si>
   <si>
     <t>&lt;tilde&gt;md-v_c</t>
+  </si>
+  <si>
+    <t>author</t>
   </si>
 </sst>
 </file>
@@ -9032,7 +9035,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8848E86-A146-4530-A694-2F38523B621A}">
-  <dimension ref="B4:J45"/>
+  <dimension ref="B4:J46"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="3" max="3" width="15.796875" bestFit="1" customWidth="1"/>
@@ -9207,7 +9210,7 @@
     </row>
     <row r="23" spans="3:10">
       <c r="C23" t="s">
-        <v>300</v>
+        <v>322</v>
       </c>
       <c r="D23" t="s">
         <v>313</v>
@@ -9215,7 +9218,7 @@
     </row>
     <row r="24" spans="3:10">
       <c r="C24" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D24" t="s">
         <v>313</v>
@@ -9223,7 +9226,7 @@
     </row>
     <row r="25" spans="3:10">
       <c r="C25" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D25" t="s">
         <v>313</v>
@@ -9231,42 +9234,39 @@
     </row>
     <row r="26" spans="3:10">
       <c r="C26" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="D26" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="27" spans="3:10" ht="13.15">
-      <c r="C27" s="3" t="s">
+    <row r="27" spans="3:10">
+      <c r="C27" t="s">
+        <v>314</v>
+      </c>
+      <c r="D27" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="28" spans="3:10" ht="13.15">
+      <c r="C28" s="3" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="30" spans="3:10">
-      <c r="C30" t="s">
+    <row r="31" spans="3:10">
+      <c r="C31" t="s">
         <v>315</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>316</v>
-      </c>
-    </row>
-    <row r="31" spans="3:10">
-      <c r="C31" s="14" t="s">
-        <v>318</v>
-      </c>
-      <c r="D31" s="14" t="s">
-        <v>304</v>
-      </c>
-      <c r="E31" s="14" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="32" spans="3:10">
       <c r="C32" s="14" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E32" s="14" t="s">
         <v>308</v>
@@ -9274,10 +9274,10 @@
     </row>
     <row r="33" spans="3:5">
       <c r="C33" s="14" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E33" s="14" t="s">
         <v>308</v>
@@ -9285,17 +9285,28 @@
     </row>
     <row r="34" spans="3:5">
       <c r="C34" s="14" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E34" s="14" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="45" spans="3:5">
-      <c r="C45" t="s">
+    <row r="35" spans="3:5">
+      <c r="C35" s="14" t="s">
+        <v>321</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="E35" s="14" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5">
+      <c r="C46" t="s">
         <v>317</v>
       </c>
     </row>
